--- a/sheets/BFSI.xlsx
+++ b/sheets/BFSI.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Business" sheetId="1" state="visible" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
   <si>
     <t xml:space="preserve">Banking, Financial Services, and Insurance.</t>
   </si>
@@ -62,6 +62,9 @@
     <t>PE</t>
   </si>
   <si>
+    <t xml:space="preserve">stock + mutual fund</t>
+  </si>
+  <si>
     <t>MOTILALOFS</t>
   </si>
   <si>
@@ -399,6 +402,9 @@
   </si>
   <si>
     <t xml:space="preserve">Network </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech based services like MF , ETF buying but the actual AUM goes to the company i.e. Aditya birla Sun life AMC </t>
   </si>
   <si>
     <t xml:space="preserve">Fees and Commision Income</t>
@@ -1856,31 +1862,34 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" ht="14.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>7071.6499999999996</v>
@@ -1903,10 +1912,10 @@
     </row>
     <row r="10" ht="14.25">
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>2924.9000000000001</v>
@@ -1949,40 +1958,40 @@
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11"/>
@@ -2009,60 +2018,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1">
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1">
@@ -2130,7 +2139,7 @@
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>60.588000000000001</v>
@@ -2248,7 +2257,7 @@
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>387.75599999999997</v>
@@ -2366,7 +2375,7 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>10.385999999999999</v>
@@ -2474,7 +2483,7 @@
     </row>
     <row r="6" s="1" customFormat="1">
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1">
         <f>SUM(C3:C5)</f>
@@ -2612,7 +2621,7 @@
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" s="6">
         <v>10.055999999999999</v>
@@ -2720,7 +2729,7 @@
     </row>
     <row r="8" s="1" customFormat="1">
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1">
         <f>C6+C7</f>
@@ -2892,7 +2901,7 @@
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" s="6">
         <v>16.423999999999999</v>
@@ -3010,7 +3019,7 @@
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="6">
         <v>117.41200000000001</v>
@@ -3128,7 +3137,7 @@
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="6">
         <v>2.9140000000000001</v>
@@ -3236,7 +3245,7 @@
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="6">
         <v>58.061</v>
@@ -3354,7 +3363,7 @@
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="6">
         <v>3.8119999999999998</v>
@@ -3472,7 +3481,7 @@
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="6">
         <v>112.291</v>
@@ -3590,7 +3599,7 @@
     </row>
     <row r="16" s="1" customFormat="1">
       <c r="B16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="10">
         <f>SUM(C10:C15)</f>
@@ -3728,7 +3737,7 @@
     </row>
     <row r="17" s="1" customFormat="1">
       <c r="B17" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="1">
         <f>C8-C16</f>
@@ -3866,7 +3875,7 @@
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="6">
         <v>-40.012</v>
@@ -4403,26 +4412,26 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F22" s="5"/>
       <c r="J22" s="5"/>
       <c r="N22" s="5"/>
       <c r="R22" s="5"/>
       <c r="AA22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AP22" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AQ22" s="13">
         <v>0.01</v>
@@ -4430,7 +4439,7 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="14">
@@ -4516,7 +4525,7 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="AP23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AQ23" s="13">
         <v>0.12</v>
@@ -4524,7 +4533,7 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="14">
@@ -4610,7 +4619,7 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="AP24" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AQ24" s="17">
         <f>Business!E10</f>
@@ -4619,7 +4628,7 @@
     </row>
     <row r="25" s="18" customFormat="1">
       <c r="B25" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -4705,7 +4714,7 @@
       <c r="AC25" s="18"/>
       <c r="AD25" s="18"/>
       <c r="AP25" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AQ25" s="24">
         <f>NPV(AQ23,AE19:CY19)</f>
@@ -4775,7 +4784,7 @@
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="14">
         <f t="shared" ref="C26:C27" si="27">C10/C3</f>
@@ -4891,7 +4900,7 @@
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" s="14">
         <f t="shared" si="27"/>
@@ -5000,7 +5009,7 @@
         <v>0.24148835356950399</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AQ27">
         <f>Business!D10</f>
@@ -5009,7 +5018,7 @@
     </row>
     <row r="28" s="18" customFormat="1">
       <c r="B28" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="20">
@@ -5092,7 +5101,7 @@
       <c r="AC28" s="18"/>
       <c r="AD28" s="18"/>
       <c r="AP28" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ28" s="26">
         <f>AQ25*10000000/AQ24</f>
@@ -5162,7 +5171,7 @@
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="27">
@@ -5250,7 +5259,7 @@
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="14">
@@ -5338,7 +5347,7 @@
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="14">
@@ -5432,7 +5441,7 @@
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="14">
@@ -5565,54 +5574,54 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" ht="14.25"/>
     <row r="3" ht="14.25">
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="B11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -5636,10 +5645,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" s="29"/>
       <c r="D1" s="29"/>
@@ -5660,40 +5669,40 @@
     </row>
     <row r="2" s="1" customFormat="1">
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1">
@@ -5768,7 +5777,7 @@
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="29">
         <v>132.22999999999999</v>
@@ -5866,7 +5875,7 @@
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="29">
         <v>300.39999999999998</v>
@@ -5964,7 +5973,7 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="29">
         <v>0.63</v>
@@ -6052,7 +6061,7 @@
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="29">
         <v>27.420000000000002</v>
@@ -6150,7 +6159,7 @@
     </row>
     <row r="7" s="1" customFormat="1">
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1">
         <f>SUM(C3:C6)</f>
@@ -6266,7 +6275,7 @@
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="29">
         <v>2.1499999999999999</v>
@@ -6357,7 +6366,7 @@
     <row r="9" s="1" customFormat="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1">
         <f>C7+C8</f>
@@ -6498,7 +6507,7 @@
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" s="29">
         <v>81.780000000000001</v>
@@ -6596,7 +6605,7 @@
     </row>
     <row r="12">
       <c r="B12" s="29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="29"/>
       <c r="D12" s="29"/>
@@ -6633,7 +6642,7 @@
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="29">
         <v>175.58000000000001</v>
@@ -6731,7 +6740,7 @@
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="29">
         <v>-3.2000000000000002</v>
@@ -6819,7 +6828,7 @@
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="29">
         <v>15.31</v>
@@ -6917,7 +6926,7 @@
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" s="29">
         <v>124.84999999999999</v>
@@ -7015,7 +7024,7 @@
     </row>
     <row r="17" s="1" customFormat="1">
       <c r="B17" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1">
         <f>SUM(C11:C16)</f>
@@ -7131,7 +7140,7 @@
     </row>
     <row r="18" s="1" customFormat="1">
       <c r="B18" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" s="1">
         <f>C9-C17</f>
@@ -7247,7 +7256,7 @@
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" s="29">
         <v>0.14000000000000001</v>
@@ -7344,7 +7353,7 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C20" s="29">
         <f>-28.12+6.52</f>
@@ -7822,7 +7831,7 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C23" s="29"/>
       <c r="D23" s="29"/>
@@ -7845,7 +7854,7 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -7868,7 +7877,7 @@
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C25" s="29">
         <v>17.18</v>
@@ -7934,21 +7943,21 @@
     <row r="27">
       <c r="F27" s="5"/>
       <c r="V27" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="14">
@@ -8007,7 +8016,7 @@
       </c>
       <c r="AD28" s="14"/>
       <c r="AK28" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AL28" s="13">
         <v>0.01</v>
@@ -8015,7 +8024,7 @@
     </row>
     <row r="29">
       <c r="B29" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="14">
@@ -8074,7 +8083,7 @@
       </c>
       <c r="AD29" s="14"/>
       <c r="AK29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AL29" s="13">
         <v>0.12</v>
@@ -8082,7 +8091,7 @@
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="14">
         <f>C11/C3</f>
@@ -8155,7 +8164,7 @@
         <v>0.54000000000000004</v>
       </c>
       <c r="AK30" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL30" s="3">
         <f>AL31*AL34/10000000</f>
@@ -8164,7 +8173,7 @@
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F31" s="5"/>
       <c r="L31" s="14"/>
@@ -8200,7 +8209,7 @@
         <v>0.12962967429938105</v>
       </c>
       <c r="AK31" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AL31" s="17">
         <f>Business!E9</f>
@@ -8209,7 +8218,7 @@
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="14">
@@ -8267,7 +8276,7 @@
         <v>0.074999999999999997</v>
       </c>
       <c r="AK32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AL32" s="3">
         <f>NPV(AL29,Z21:CQ21)</f>
@@ -8276,7 +8285,7 @@
     </row>
     <row r="33">
       <c r="B33" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="14">
@@ -8335,7 +8344,7 @@
       </c>
       <c r="AF33" s="14"/>
       <c r="AK33" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AL33" s="3">
         <f>AL32*10000000/AL31</f>
@@ -8344,7 +8353,7 @@
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="14">
@@ -8404,7 +8413,7 @@
         <v>0.28014679035206225</v>
       </c>
       <c r="AK34" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AL34">
         <f>Business!D9</f>
@@ -8413,7 +8422,7 @@
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C35" s="14">
         <f>C20/C18*-1</f>
@@ -8490,7 +8499,7 @@
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F36" s="5"/>
       <c r="X36" s="14">
@@ -8526,39 +8535,44 @@
   </cols>
   <sheetData>
     <row r="2" ht="14.25">
-      <c r="B2" t="s">
-        <v>119</v>
+      <c r="B2" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="3" ht="14.25"/>
     <row r="4" ht="14.25">
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="B5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="B6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="B7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="B8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="B9" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="B11" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -8578,7 +8592,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -8591,7 +8605,7 @@
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3">
         <v>14290.58</v>
@@ -8599,7 +8613,7 @@
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4">
         <v>2.7200000000000002</v>
@@ -8607,7 +8621,7 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>1348.54</v>
@@ -8615,7 +8629,7 @@
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C6">
         <v>362.13</v>
@@ -8623,7 +8637,7 @@
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C7">
         <v>58.979999999999997</v>
@@ -8631,7 +8645,7 @@
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8">
         <v>486.43000000000001</v>
@@ -8639,7 +8653,7 @@
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9">
         <v>17950.07</v>
@@ -8647,7 +8661,7 @@
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -8655,7 +8669,7 @@
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C11">
         <v>6.0899999999999999</v>
@@ -8684,7 +8698,7 @@
   <sheetData>
     <row r="1" ht="16.5">
       <c r="A1" s="34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" ht="14.25">
@@ -8692,147 +8706,147 @@
     </row>
     <row r="3" ht="16.5">
       <c r="B3" s="34" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" ht="16.5">
       <c r="B4" s="34" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" ht="16.5">
       <c r="B5" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" ht="16.5">
       <c r="B6" s="34" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" ht="16.5">
       <c r="B7" s="34" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" ht="16.5">
       <c r="B8" s="34" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" ht="16.5">
       <c r="B9" s="34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="16.5">
       <c r="B10" s="34" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" ht="16.5">
       <c r="B11" s="34" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" ht="16.5">
       <c r="B12" s="34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" ht="16.5">
       <c r="B13" s="34" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" ht="16.5">
       <c r="B17" s="35" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" ht="16.5">
       <c r="B18" s="34"/>
       <c r="D18" s="34" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="D19" s="34" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="D20" s="34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="D21" s="34" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="D22" s="34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="B24" s="35" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" ht="14.25">
       <c r="D25" s="34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" ht="14.25">
       <c r="D26" s="34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" ht="14.25">
       <c r="D28" s="34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E28" s="34"/>
       <c r="G28" s="34" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" ht="14.25">
       <c r="D29" s="34" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="D30" s="34" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" ht="14.25">
       <c r="D31" s="34" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" ht="14.25">
       <c r="D32" s="34" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -8859,10 +8873,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C1" s="29"/>
       <c r="D1" s="29"/>
@@ -8881,66 +8895,66 @@
       <c r="Y1" s="29"/>
       <c r="Z1" s="29"/>
       <c r="AA1" s="29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AE1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1">
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="29">
         <v>211.97999999999999</v>
@@ -9161,7 +9175,7 @@
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C4" s="29">
         <v>0.13</v>
@@ -9285,7 +9299,7 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C5" s="29">
         <v>0.01</v>
@@ -9409,10 +9423,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C6" s="29">
         <v>568.94000000000005</v>
@@ -9536,7 +9550,7 @@
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C7" s="29">
         <v>106.06999999999999</v>
@@ -9660,7 +9674,7 @@
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C8" s="29">
         <v>11.619999999999999</v>
@@ -9784,7 +9798,7 @@
     </row>
     <row r="9" s="1" customFormat="1">
       <c r="B9" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C9" s="1">
         <f>C3+C5+C6</f>
@@ -9936,7 +9950,7 @@
     </row>
     <row r="10" s="1" customFormat="1">
       <c r="B10" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C10" s="1">
         <f>SUM(C3:C8)</f>
@@ -10100,7 +10114,7 @@
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="6">
         <v>2.5099999999999998</v>
@@ -10229,7 +10243,7 @@
     </row>
     <row r="12" s="1" customFormat="1">
       <c r="B12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1">
         <f>C10+C11</f>
@@ -10399,7 +10413,7 @@
     </row>
     <row r="13" s="0" customFormat="1">
       <c r="B13" s="29" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -10441,7 +10455,7 @@
     </row>
     <row r="14" s="1" customFormat="1">
       <c r="B14" s="29" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -10532,7 +10546,7 @@
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C16" s="6">
         <v>106.19</v>
@@ -10671,7 +10685,7 @@
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C17" s="6">
         <v>196.75999999999999</v>
@@ -10810,7 +10824,7 @@
     </row>
     <row r="18">
       <c r="B18" s="29" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C18" s="6">
         <v>0</v>
@@ -10907,10 +10921,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C19" s="6">
         <v>42.479999999999997</v>
@@ -11019,7 +11033,7 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="6">
         <v>180.37</v>
@@ -11158,7 +11172,7 @@
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="6">
         <v>11.26</v>
@@ -11297,7 +11311,7 @@
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C22" s="6">
         <v>78.469999999999999</v>
@@ -11436,7 +11450,7 @@
     </row>
     <row r="23" s="1" customFormat="1">
       <c r="B23" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C23" s="1">
         <f>SUM(C16:C22)</f>
@@ -11606,7 +11620,7 @@
     </row>
     <row r="24" s="0" customFormat="1">
       <c r="B24" s="29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C24" s="6">
         <v>0</v>
@@ -11735,7 +11749,7 @@
     </row>
     <row r="25" s="1" customFormat="1">
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="10">
         <f>C12-C23+C24</f>
@@ -11905,7 +11919,7 @@
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="6">
         <f>-65.63</f>
@@ -12472,7 +12486,7 @@
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="6">
         <v>1.1200000000000001</v>
@@ -12577,7 +12591,7 @@
     </row>
     <row r="29" s="37" customFormat="1">
       <c r="B29" s="37" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -12641,7 +12655,7 @@
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -12723,7 +12737,7 @@
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C32" s="6"/>
       <c r="E32" s="29"/>
@@ -12778,7 +12792,7 @@
         <v>148272290</v>
       </c>
       <c r="AV32" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AW32" s="13">
         <v>0.01</v>
@@ -12786,7 +12800,7 @@
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C33" s="6">
         <v>15.07</v>
@@ -12874,7 +12888,7 @@
         <v>41.829999999999998</v>
       </c>
       <c r="AV33" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AW33" s="13">
         <v>0.12</v>
@@ -12882,7 +12896,7 @@
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="29"/>
@@ -12946,7 +12960,7 @@
         <v>168.7193203800926</v>
       </c>
       <c r="AV34" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AW34" s="3">
         <f>NPV(AW33,AL27:DD27)</f>
@@ -12955,7 +12969,7 @@
     </row>
     <row r="35">
       <c r="B35" s="29" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C35" s="8"/>
       <c r="F35" s="5"/>
@@ -13009,7 +13023,7 @@
         <v>602.35000000000002</v>
       </c>
       <c r="AV35" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AW35">
         <v>598642630</v>
@@ -13044,7 +13058,7 @@
       <c r="AK36" s="8"/>
       <c r="AL36" s="29"/>
       <c r="AV36" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AW36" s="3">
         <f>AW34*10000000/AW35</f>
@@ -13053,7 +13067,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F37" s="5"/>
       <c r="AA37" s="6"/>
@@ -13063,17 +13077,17 @@
       <c r="AE37" s="6"/>
       <c r="AG37" s="6"/>
       <c r="AH37" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AI37" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AJ37" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AK37" s="10"/>
       <c r="AV37" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AW37" s="3">
         <v>822.89999999999998</v>
@@ -13081,7 +13095,7 @@
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C38" s="14">
         <f>C16/C3</f>
@@ -13195,7 +13209,7 @@
     </row>
     <row r="39">
       <c r="B39" s="29" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C39" s="14">
         <f>C17/C6</f>
@@ -13313,7 +13327,7 @@
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C40" s="16">
         <f>1-C38</f>
@@ -13419,7 +13433,7 @@
     </row>
     <row r="41" ht="14.25">
       <c r="B41" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C41" s="29"/>
       <c r="D41" s="14"/>
@@ -13537,7 +13551,7 @@
     </row>
     <row r="42" ht="14.25">
       <c r="B42" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -13653,7 +13667,7 @@
     </row>
     <row r="43" ht="14.25">
       <c r="B43" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -13769,7 +13783,7 @@
     </row>
     <row r="44" s="0" customFormat="1" ht="14.25">
       <c r="B44" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -13863,7 +13877,7 @@
     </row>
     <row r="45" s="0" customFormat="1" ht="14.25">
       <c r="B45" s="29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C45" s="29"/>
       <c r="D45" s="6"/>
@@ -13957,7 +13971,7 @@
     </row>
     <row r="46" s="0" customFormat="1" ht="14.25">
       <c r="B46" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -14021,7 +14035,7 @@
     </row>
     <row r="48" ht="14.25">
       <c r="B48" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C48" s="29"/>
       <c r="D48" s="14"/>
@@ -14139,7 +14153,7 @@
     </row>
     <row r="49" ht="14.25">
       <c r="B49" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C49" s="29"/>
       <c r="D49" s="32"/>
@@ -14257,7 +14271,7 @@
     </row>
     <row r="50" ht="14.25">
       <c r="B50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C50" s="29"/>
       <c r="D50" s="32"/>
@@ -14375,7 +14389,7 @@
     </row>
     <row r="51" ht="14.25">
       <c r="B51" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C51" s="14">
         <f>C26/C25*-1</f>
@@ -14509,20 +14523,20 @@
     </row>
     <row r="53" ht="14.25">
       <c r="A53" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F53" s="5"/>
     </row>
     <row r="54" ht="14.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AM54" s="13"/>
     </row>
     <row r="55" ht="14.25">
       <c r="B55" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C55">
         <v>512.04999999999995</v>
@@ -14530,7 +14544,7 @@
     </row>
     <row r="56" ht="14.25">
       <c r="B56" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C56">
         <v>110.84</v>
@@ -14538,10 +14552,10 @@
     </row>
     <row r="57" ht="14.25">
       <c r="A57" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B57" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C57">
         <v>205.33000000000001</v>
@@ -14549,7 +14563,7 @@
     </row>
     <row r="58" ht="14.25">
       <c r="B58" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C58">
         <v>1.2</v>
@@ -14557,7 +14571,7 @@
     </row>
     <row r="59" ht="14.25">
       <c r="B59" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C59">
         <v>136.84999999999999</v>
@@ -14566,7 +14580,7 @@
     </row>
     <row r="60" ht="14.25">
       <c r="B60" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C60">
         <v>0.16</v>
@@ -14575,7 +14589,7 @@
     </row>
     <row r="61" s="1" customFormat="1" ht="14.25">
       <c r="B61" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C61" s="1">
         <f>SUM(C55:C60)</f>
@@ -14602,13 +14616,13 @@
     </row>
     <row r="63" ht="14.25">
       <c r="B63" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F63" s="5"/>
     </row>
     <row r="64" ht="14.25">
       <c r="B64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C64">
         <v>114.7</v>
@@ -14617,7 +14631,7 @@
     </row>
     <row r="65" ht="14.25">
       <c r="B65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -14625,7 +14639,7 @@
     </row>
     <row r="66" ht="14.25">
       <c r="B66" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C66">
         <v>103.88</v>
@@ -14633,7 +14647,7 @@
     </row>
     <row r="67" ht="14.25">
       <c r="B67" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C67">
         <v>77.540000000000006</v>
@@ -14641,7 +14655,7 @@
     </row>
     <row r="68" ht="14.25">
       <c r="B68" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C68">
         <v>-2.4900000000000002</v>
@@ -14650,7 +14664,7 @@
     </row>
     <row r="69" ht="14.25">
       <c r="B69" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C69">
         <v>11.35</v>
@@ -14659,7 +14673,7 @@
     </row>
     <row r="70" ht="14.25">
       <c r="B70" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C70">
         <v>-17.510000000000002</v>
@@ -14668,7 +14682,7 @@
     </row>
     <row r="71" s="1" customFormat="1" ht="14.25">
       <c r="B71" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C71" s="1">
         <f>SUM(C65:C70)</f>
